--- a/data/trans_orig/P34B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34B01-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población camina durante más de 30 minutos</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población camina (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 3,67</t>
+          <t>3,3; 3,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,49</t>
+          <t>3,06; 3,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,69</t>
+          <t>3,17; 3,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 2,96</t>
+          <t>2,66; 2,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 2,96</t>
+          <t>2,6; 2,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 2,72</t>
+          <t>2,4; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,23</t>
+          <t>2,97; 3,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,13</t>
+          <t>2,84; 3,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,06</t>
+          <t>2,76; 3,04</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,48</t>
+          <t>2,21; 2,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 3,42</t>
+          <t>3,15; 3,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,87</t>
+          <t>2,73; 3,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,27 +807,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 3,36</t>
+          <t>3,1; 3,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 3,83</t>
+          <t>3,39; 3,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 2,68</t>
+          <t>2,51; 2,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,34</t>
+          <t>3,15; 3,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,78</t>
+          <t>3,12; 3,78</t>
         </is>
       </c>
     </row>
@@ -897,27 +897,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,39</t>
+          <t>1,85; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,67</t>
+          <t>3,18; 3,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,35</t>
+          <t>3,9; 4,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,26</t>
+          <t>2,76; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 3,83</t>
+          <t>3,33; 3,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 3,68</t>
+          <t>3,33; 3,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 4,06</t>
+          <t>3,75; 4,06</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,4</t>
+          <t>3,2; 3,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,86</t>
+          <t>3,0; 3,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 2,97</t>
+          <t>2,78; 2,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,25</t>
+          <t>3,04; 3,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 3,53</t>
+          <t>3,3; 3,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 2,82</t>
+          <t>2,69; 2,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,3</t>
+          <t>3,15; 3,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 3,65</t>
+          <t>3,22; 3,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34B01-Estudios-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>2,92</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,69</t>
+          <t>3,29; 3,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,48</t>
+          <t>3,05; 3,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,68</t>
+          <t>3,14; 3,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 2,98</t>
+          <t>2,6; 2,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 2,71</t>
+          <t>2,44; 2,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,22</t>
+          <t>2,98; 3,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,12</t>
+          <t>2,85; 3,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,04</t>
+          <t>2,77; 3,06</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,9</t>
         </is>
       </c>
     </row>
@@ -787,37 +787,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,48</t>
+          <t>2,2; 2,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,43</t>
+          <t>3,16; 3,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,88</t>
+          <t>3,79; 4,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,02</t>
+          <t>2,73; 3,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 3,36</t>
+          <t>3,09; 3,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 3,84</t>
+          <t>3,76; 3,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,69</t>
+          <t>2,49; 2,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 3,78</t>
+          <t>3,81; 3,99</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>3,96</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,4</t>
+          <t>1,89; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -907,37 +907,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,34</t>
+          <t>3,94; 4,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,29</t>
+          <t>2,75; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 3,8</t>
+          <t>3,33; 3,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 3,88</t>
+          <t>3,58; 3,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,75</t>
+          <t>2,36; 2,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 3,67</t>
+          <t>3,32; 3,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 4,06</t>
+          <t>3,81; 4,09</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,72</t>
         </is>
       </c>
     </row>
@@ -1012,32 +1012,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,41</t>
+          <t>3,2; 3,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,86</t>
+          <t>3,78; 3,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 2,97</t>
+          <t>2,78; 2,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,26</t>
+          <t>3,06; 3,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,54</t>
+          <t>3,48; 3,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 2,83</t>
+          <t>2,68; 2,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 3,65</t>
+          <t>3,65; 3,79</t>
         </is>
       </c>
     </row>
